--- a/data/raw/okra_biochar_data.xlsx
+++ b/data/raw/okra_biochar_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\autocade\review article material\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\-Effects-of-Mixed-Wood-Biochar-on-Fertilizer-Use-Efficiency-and-Growth-Performance-of-Okra\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3324FBB0-DC8C-40C4-8B7B-6818F08F3FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C3284A-F547-4B06-B754-C57F5013F537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="861" activeTab="3" xr2:uid="{AA095818-A5E7-4844-AF07-510536A3E191}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="861" activeTab="6" xr2:uid="{AA095818-A5E7-4844-AF07-510536A3E191}"/>
   </bookViews>
   <sheets>
     <sheet name="Plant Height" sheetId="3" r:id="rId1"/>
@@ -43,6 +43,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -19318,12 +19321,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
     <mergeCell ref="D14:D16"/>
     <mergeCell ref="E14:E16"/>
     <mergeCell ref="F14:F16"/>
@@ -19333,6 +19330,12 @@
     <mergeCell ref="D11:D13"/>
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19681,6 +19684,375 @@
       </c>
       <c r="C16">
         <v>11.87</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26887E06-5EB8-44D5-A7C8-8325549D3974}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.43</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>0.43433333333333329</v>
+      </c>
+      <c r="E2" s="6">
+        <f>STDEV(C2:C4)</f>
+        <v>3.3709543653590621E-2</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>1.9485285348896313E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.47</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.217</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>0.254</v>
+      </c>
+      <c r="E5" s="7">
+        <f>STDEV(C5:C7)</f>
+        <v>3.9153543900903517E-2</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="1">E5/1.73</f>
+        <v>2.26321063011003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.41</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="2">AVERAGE(C8:C10)</f>
+        <v>0.45799999999999996</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" ref="E8" si="3">STDEV(C8:C10)</f>
+        <v>4.1617304093369632E-2</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="4">E8/1.73</f>
+        <v>2.4056245140676089E-2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>0.43433333333333329</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>3.3709543653590621E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.48</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>0.254</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>3.9153543900903517E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="5">AVERAGE(C11:C13)</f>
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ref="E11" si="6">STDEV(C11:C13)</f>
+        <v>3.5510561809129412E-2</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="7">E11/1.73</f>
+        <v>2.0526336305855153E-2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>0.45799999999999996</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>4.1617304093369632E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>3.5510561809129412E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>0.60733333333333339</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>2.3007245235649884E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="8">AVERAGE(C14:C16)</f>
+        <v>0.60733333333333339</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" ref="E14" si="9">STDEV(C14:C16)</f>
+        <v>2.3007245235649884E-2</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="10">E14/1.73</f>
+        <v>1.3298985685346754E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.63</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
@@ -19710,8 +20082,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26887E06-5EB8-44D5-A7C8-8325549D3974}">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FE1F26-351E-4CB8-9260-BF034A5705D5}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -19726,9 +20098,6 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
@@ -19746,20 +20115,20 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
-        <v>0.43</v>
+      <c r="C2">
+        <v>0.23400000000000001</v>
       </c>
       <c r="D2" s="6">
         <f>AVERAGE(C2:C4)</f>
-        <v>0.43433333333333329</v>
+        <v>0.28066666666666668</v>
       </c>
       <c r="E2" s="6">
         <f>STDEV(C2:C4)</f>
-        <v>3.3709543653590621E-2</v>
+        <v>4.0857475856118597E-2</v>
       </c>
       <c r="F2" s="7">
         <f>E2/1.73</f>
-        <v>1.9485285348896313E-2</v>
+        <v>2.3617038067120576E-2</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -19769,8 +20138,8 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
-        <v>0.40300000000000002</v>
+      <c r="C3">
+        <v>0.31</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -19783,8 +20152,8 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="4">
-        <v>0.47</v>
+      <c r="C4">
+        <v>0.29799999999999999</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -19797,20 +20166,20 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="4">
-        <v>0.217</v>
+      <c r="C5">
+        <v>0.56999999999999995</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>0.254</v>
-      </c>
-      <c r="E5" s="7">
-        <f>STDEV(C5:C7)</f>
-        <v>3.9153543900903517E-2</v>
+        <v>0.59133333333333338</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>1.8502252115170575E-2</v>
       </c>
       <c r="F5" s="7">
-        <f t="shared" ref="F5" si="1">E5/1.73</f>
-        <v>2.26321063011003E-2</v>
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>1.0694943419173743E-2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -19820,8 +20189,1853 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="4">
-        <v>0.25</v>
+      <c r="C6">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0.49</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>0.50233333333333341</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>1.1590225767142484E-2</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>6.6995524665563492E-3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0.504</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>0.28066666666666668</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>4.0857475856118597E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>0.59133333333333338</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>1.8502252115170575E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0.50900000000000001</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>0.5073333333333333</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>1.6563010998406472E-2</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>9.5739947967667469E-3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>0.50233333333333341</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>1.1590225767142484E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>0.49</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>0.5073333333333333</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>1.6563010998406472E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>0.90333333333333332</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>3.5118845842842437E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0.87</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>0.90333333333333332</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>3.5118845842842437E-2</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>2.0299910891816438E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0.9</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>0.94</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8149C50-947B-4F32-8B7A-55F22EABDA0E}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0.81</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>0.73999999999999988</v>
+      </c>
+      <c r="E2" s="6">
+        <f>STDEV(C2:C4)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>4.0462427745664747E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0.67</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0.74</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1.2982</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>1.2475666666666667</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>7.8366468169321829E-2</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>4.5298536514058858E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1.2871999999999999</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1.1573</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1.0165999999999999</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>1.0533000000000001</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>6.3047363148667893E-2</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>3.6443562513680861E-2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1.1261000000000001</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>0.73999999999999988</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>1.0172000000000001</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>1.2475666666666667</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>7.8366468169321829E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1.2674000000000001</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>1.2407000000000001</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>2.51334438547526E-2</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>1.4528002228180695E-2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>1.0533000000000001</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>6.3047363148667893E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>1.2175</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>1.2407000000000001</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>2.51334438547526E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>1.2372000000000001</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>1.3037666666666665</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>1.1547438388375733E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1.2971999999999999</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>1.3037666666666665</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>1.1547438388375733E-2</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>6.674819877673834E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1.3170999999999999</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>1.2969999999999999</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049DAB7E-34A2-4711-BCDA-47CE19215AC4}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="E2" s="6">
+        <f>STDEV(C2:C4)</f>
+        <v>7.5425459892532312E-2</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>4.3598531729787462E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0.755</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1.171</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>1.113</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>5.302829433425145E-2</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>3.0652193256792745E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1.0669999999999999</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1.101</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1.02</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>0.96500000000000019</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>0.14930170796075776</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>8.6301565295235694E-2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1.079</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>7.5425459892532312E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>0.79600000000000004</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>1.113</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>5.302829433425145E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1.1970000000000001</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>1.133</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>5.8923679450624995E-2</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>3.4059930318280342E-2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>0.96500000000000019</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>0.14930170796075776</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>1.081</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>1.133</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>5.8923679450624995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>1.121</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>2.4248711305964205E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1.1419999999999999</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>2.4248711305964205E-2</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>1.4016596130615148E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1.1240000000000001</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>1.0940000000000001</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC084203-75CD-44F8-9605-0E76FFF67A2B}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>9.5000000000000015E-2</v>
+      </c>
+      <c r="E2" s="6">
+        <f>STDEV(C2:C4)</f>
+        <v>5.2915026221291859E-3</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>3.0586720359128241E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>2.0000000000000018E-3</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>1.1560693641618507E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0.129</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0.121</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>0.11566666666666665</v>
+      </c>
+      <c r="E8" s="6">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>7.5718777944003635E-3</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>4.3768079736418285E-3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0.11899999999999999</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>9.5000000000000015E-2</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>5.2915026221291859E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>0.107</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>2.0000000000000018E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0.152</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>0.13066666666666668</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>2.0550750189064392E-2</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>1.1879046352060342E-2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>0.11566666666666665</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>7.5718777944003635E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>0.129</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>0.13066666666666668</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>2.0550750189064392E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>0.111</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>0.16033333333333333</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>2.7227437142216249E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0.191</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>0.16033333333333333</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>2.7227437142216249E-2</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>1.5738402972379335E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>0.151</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975E62B9-E4A7-4D06-8781-56D58217A609}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D2" s="8">
+        <f>AVERAGE(C2:C4)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E2" s="8">
+        <f>STDEV(C2:C4)</f>
+        <v>5.000000000000001E-3</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>2.890173410404625E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>0.01</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0.02</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="D5" s="8">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>3.8666666666666669E-2</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>6.1101009266077855E-3</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>3.5318502465940958E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0.04</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="D8" s="8">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>0.14233333333333334</v>
+      </c>
+      <c r="E8" s="8">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>7.76745346515402E-3</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>4.4898574943086824E-3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0.151</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="5">
+        <f>D2</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>5.000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="5">
+        <f>D5</f>
+        <v>3.8666666666666669E-2</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>6.1101009266077855E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0.125</v>
+      </c>
+      <c r="D11" s="8">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>0.11833333333333333</v>
+      </c>
+      <c r="E11" s="8">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>7.6376261582597324E-3</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>4.4148128082426201E-3</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5">
+        <f>D8</f>
+        <v>0.14233333333333334</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>7.76745346515402E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>0.11</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="5">
+        <f>D11</f>
+        <v>0.11833333333333333</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>7.6376261582597324E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>0.12</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="5">
+        <f>D14</f>
+        <v>0.19033333333333333</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>7.2341781380702418E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="D14" s="8">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>0.19033333333333333</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>7.2341781380702418E-3</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>4.181605860156209E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>0.182</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F62340-CD4B-4BE3-B13A-8440BC2B3C42}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>4.6050000000000004</v>
+      </c>
+      <c r="E2" s="7">
+        <f>STDEV(C2:C4)</f>
+        <v>3.726452736853104</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>2.1540189230364764</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1.97</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>7.24</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5.13</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>3.4899999999999998</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>2.686186888509436</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>1.5527091841095007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0.39</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="7"/>
@@ -19834,8 +22048,8 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="4">
-        <v>0.29499999999999998</v>
+      <c r="C7">
+        <v>4.95</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="7"/>
@@ -19848,26 +22062,26 @@
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="4">
-        <v>0.41</v>
+      <c r="C8">
+        <v>2.73</v>
       </c>
       <c r="D8" s="6">
-        <f t="shared" ref="D8" si="2">AVERAGE(C8:C10)</f>
-        <v>0.45799999999999996</v>
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>2.6</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" ref="E8" si="3">STDEV(C8:C10)</f>
-        <v>4.1617304093369632E-2</v>
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>1.2500799974401644</v>
       </c>
       <c r="F8" s="7">
-        <f t="shared" ref="F8" si="4">E8/1.73</f>
-        <v>2.4056245140676089E-2</v>
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>0.72258959389604882</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -19877,8 +22091,8 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="4">
-        <v>0.48399999999999999</v>
+      <c r="C9">
+        <v>3.78</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
@@ -19888,11 +22102,11 @@
       </c>
       <c r="J9" s="1">
         <f>D2</f>
-        <v>0.43433333333333329</v>
+        <v>4.6050000000000004</v>
       </c>
       <c r="K9">
         <f>E2</f>
-        <v>3.3709543653590621E-2</v>
+        <v>3.726452736853104</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -19902,8 +22116,8 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" s="4">
-        <v>0.48</v>
+      <c r="C10">
+        <v>1.29</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
@@ -19913,11 +22127,11 @@
       </c>
       <c r="J10" s="1">
         <f>D5</f>
-        <v>0.254</v>
+        <v>3.4899999999999998</v>
       </c>
       <c r="K10">
         <f>E5</f>
-        <v>3.9153543900903517E-2</v>
+        <v>2.686186888509436</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -19927,31 +22141,31 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="4">
-        <v>0.39900000000000002</v>
+      <c r="C11">
+        <v>4.2300000000000004</v>
       </c>
       <c r="D11" s="6">
-        <f t="shared" ref="D11" si="5">AVERAGE(C11:C13)</f>
-        <v>0.36299999999999999</v>
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>3.4000000000000004</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" ref="E11" si="6">STDEV(C11:C13)</f>
-        <v>3.5510561809129412E-2</v>
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>2.0454583838347826</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" ref="F11" si="7">E11/1.73</f>
-        <v>2.0526336305855153E-2</v>
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>1.182345886609701</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="1">
         <f>D8</f>
-        <v>0.45799999999999996</v>
+        <v>2.6</v>
       </c>
       <c r="K11">
         <f>E8</f>
-        <v>4.1617304093369632E-2</v>
+        <v>1.2500799974401644</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -19961,8 +22175,8 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12" s="4">
-        <v>0.32800000000000001</v>
+      <c r="C12">
+        <v>1.07</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
@@ -19972,11 +22186,11 @@
       </c>
       <c r="J12" s="1">
         <f>D11</f>
-        <v>0.36299999999999999</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="K12">
         <f>E11</f>
-        <v>3.5510561809129412E-2</v>
+        <v>2.0454583838347826</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -19986,8 +22200,8 @@
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13" s="4">
-        <v>0.36199999999999999</v>
+      <c r="C13">
+        <v>4.9000000000000004</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
@@ -19997,11 +22211,11 @@
       </c>
       <c r="J13" s="1">
         <f>D14</f>
-        <v>0.60733333333333339</v>
+        <v>1.07</v>
       </c>
       <c r="K13">
         <f>E14</f>
-        <v>2.3007245235649884E-2</v>
+        <v>1.1170049238924598</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -20011,20 +22225,20 @@
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="4">
-        <v>0.60799999999999998</v>
+      <c r="C14">
+        <v>0.63</v>
       </c>
       <c r="D14" s="6">
-        <f t="shared" ref="D14" si="8">AVERAGE(C14:C16)</f>
-        <v>0.60733333333333339</v>
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>1.07</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" ref="E14" si="9">STDEV(C14:C16)</f>
-        <v>2.3007245235649884E-2</v>
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>1.1170049238924598</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" ref="F14" si="10">E14/1.73</f>
-        <v>1.3298985685346754E-2</v>
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>0.64566758606500563</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -20034,8 +22248,8 @@
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="4">
-        <v>0.58399999999999996</v>
+      <c r="C15">
+        <v>0.24</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="7"/>
@@ -20048,8 +22262,744 @@
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16" s="4">
-        <v>0.63</v>
+      <c r="C16">
+        <v>2.34</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F91474D-2594-4106-AE97-A03B90325336}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>28</v>
+      </c>
+      <c r="E2" s="7">
+        <f>STDEV(C2:C4)</f>
+        <v>4</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>2.3121387283236996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>24</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>2.3094010767585034</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>1.334913917201447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>2.0816659994661331</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>1.2032751442000769</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>28</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>2.3094010767585034</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>24</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>6.1101009266077853</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>3.5318502465940957</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>2.0816659994661331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>16</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>17.333333333333332</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>6.1101009266077853</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>18</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>8.8881944173155887</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>28</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>18</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>8.8881944173155887</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>5.1376846342864679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>15</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D3B4B9-8DED-4B73-93B7-BCD80CB04959}">
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D2" s="6">
+        <f>AVERAGE(C2:C4)</f>
+        <v>2.6966666666666668</v>
+      </c>
+      <c r="E2" s="7">
+        <f>STDEV(C2:C4)</f>
+        <v>0.59601454120963582</v>
+      </c>
+      <c r="F2" s="7">
+        <f>E2/1.73</f>
+        <v>0.34451707584372016</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3.08</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3.1</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
+        <v>3.2833333333333332</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
+        <v>0.31754264805429405</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" ref="F5" si="2">E5/1.73</f>
+        <v>0.18355066361519887</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3.1</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>3.65</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3.6</v>
+      </c>
+      <c r="D8" s="6">
+        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
+        <v>3.6999999999999997</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
+        <v>0.26457513110645903</v>
+      </c>
+      <c r="F8" s="7">
+        <f t="shared" ref="F8" si="5">E8/1.73</f>
+        <v>0.15293360179564106</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3.5</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
+        <f>D2</f>
+        <v>2.6966666666666668</v>
+      </c>
+      <c r="K9">
+        <f>E2</f>
+        <v>0.59601454120963582</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <f>D5</f>
+        <v>3.2833333333333332</v>
+      </c>
+      <c r="K10">
+        <f>E5</f>
+        <v>0.31754264805429405</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>3.9</v>
+      </c>
+      <c r="D11" s="6">
+        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
+        <v>3.56</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
+        <v>0.50477717856495796</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" ref="F11" si="8">E11/1.73</f>
+        <v>0.29177871593350174</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <f>D8</f>
+        <v>3.6999999999999997</v>
+      </c>
+      <c r="K11">
+        <f>E8</f>
+        <v>0.26457513110645903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>3.8</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="I12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="1">
+        <f>D11</f>
+        <v>3.56</v>
+      </c>
+      <c r="K12">
+        <f>E11</f>
+        <v>0.50477717856495796</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>2.98</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="I13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <f>D14</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="K13">
+        <f>E14</f>
+        <v>0.66583281184793797</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>2.9</v>
+      </c>
+      <c r="D14" s="6">
+        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
+        <v>0.66583281184793797</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" ref="F14" si="11">E14/1.73</f>
+        <v>0.38487445771557111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>4.0999999999999996</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="7"/>
@@ -20079,8 +23029,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FE1F26-351E-4CB8-9260-BF034A5705D5}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDA2AF0-16A6-4B39-87FB-8E571EBB2CCD}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -20095,6 +23045,9 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
@@ -20113,19 +23066,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.23400000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="D2" s="6">
         <f>AVERAGE(C2:C4)</f>
-        <v>0.28066666666666668</v>
-      </c>
-      <c r="E2" s="6">
+        <v>0.78666666666666674</v>
+      </c>
+      <c r="E2" s="7">
         <f>STDEV(C2:C4)</f>
-        <v>4.0857475856118597E-2</v>
+        <v>0.10503967504392438</v>
       </c>
       <c r="F2" s="7">
         <f>E2/1.73</f>
-        <v>2.3617038067120576E-2</v>
+        <v>6.0716575169898486E-2</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -20136,10 +23089,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0.31</v>
+        <v>0.89</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:11">
@@ -20150,10 +23103,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.29799999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:11">
@@ -20164,19 +23117,19 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0.56999999999999995</v>
+        <v>1.2</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>0.59133333333333338</v>
-      </c>
-      <c r="E5" s="6">
+        <v>1.0733333333333335</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>1.8502252115170575E-2</v>
+        <v>0.15534906930308059</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>1.0694943419173743E-2</v>
+        <v>8.9797149886173752E-2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -20187,10 +23140,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0.60299999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:11">
@@ -20201,10 +23154,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>0.60099999999999998</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:11">
@@ -20215,25 +23168,25 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.49</v>
+        <v>1.3</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>0.50233333333333341</v>
-      </c>
-      <c r="E8" s="6">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>1.1590225767142484E-2</v>
+        <v>0.15620499351813161</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>6.6995524665563492E-3</v>
+        <v>9.0291903767706128E-2</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -20244,21 +23197,21 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>0.504</v>
+        <v>1.02</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="I9" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="1">
         <f>D2</f>
-        <v>0.28066666666666668</v>
+        <v>0.78666666666666674</v>
       </c>
       <c r="K9">
         <f>E2</f>
-        <v>4.0857475856118597E-2</v>
+        <v>0.10503967504392438</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -20269,21 +23222,21 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>0.51300000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="I10" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="1">
         <f>D5</f>
-        <v>0.59133333333333338</v>
+        <v>1.0733333333333335</v>
       </c>
       <c r="K10">
         <f>E5</f>
-        <v>1.8502252115170575E-2</v>
+        <v>0.15534906930308059</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -20294,30 +23247,30 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.50900000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>0.5073333333333333</v>
-      </c>
-      <c r="E11" s="6">
+        <v>1.5733333333333333</v>
+      </c>
+      <c r="E11" s="7">
         <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>1.6563010998406472E-2</v>
+        <v>0.31005375877956043</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>9.5739947967667469E-3</v>
+        <v>0.17922182588413899</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="1">
         <f>D8</f>
-        <v>0.50233333333333341</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="K11">
         <f>E8</f>
-        <v>1.1590225767142484E-2</v>
+        <v>0.15620499351813161</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -20328,21 +23281,21 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>0.49</v>
+        <v>1.8</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="I12" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="1">
         <f>D11</f>
-        <v>0.5073333333333333</v>
+        <v>1.5733333333333333</v>
       </c>
       <c r="K12">
         <f>E11</f>
-        <v>1.6563010998406472E-2</v>
+        <v>0.31005375877956043</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -20353,21 +23306,21 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>0.52300000000000002</v>
+        <v>1.7</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" s="1">
         <f>D14</f>
-        <v>0.90333333333333332</v>
+        <v>1.7</v>
       </c>
       <c r="K13">
         <f>E14</f>
-        <v>3.5118845842842437E-2</v>
+        <v>0.26457513110645958</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -20378,19 +23331,19 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>0.87</v>
+        <v>1.8</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>0.90333333333333332</v>
-      </c>
-      <c r="E14" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>3.5118845842842437E-2</v>
+        <v>0.26457513110645958</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>2.0299910891816438E-2</v>
+        <v>0.15293360179564139</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -20401,10 +23354,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:11">
@@ -20415,10 +23368,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>0.94</v>
+        <v>1.9</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
   </sheetData>
@@ -20445,8 +23398,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8149C50-947B-4F32-8B7A-55F22EABDA0E}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376CE82E-C44D-4C61-BB92-E28C40E3BFA2}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -20462,7 +23415,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -20482,19 +23435,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.81</v>
+        <v>14</v>
       </c>
       <c r="D2" s="6">
         <f>AVERAGE(C2:C4)</f>
-        <v>0.73999999999999988</v>
-      </c>
-      <c r="E2" s="6">
+        <v>14.9</v>
+      </c>
+      <c r="E2" s="7">
         <f>STDEV(C2:C4)</f>
-        <v>7.0000000000000007E-2</v>
+        <v>0.78102496759066575</v>
       </c>
       <c r="F2" s="7">
         <f>E2/1.73</f>
-        <v>4.0462427745664747E-2</v>
+        <v>0.45145951883853513</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -20505,10 +23458,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0.67</v>
+        <v>15.4</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:11">
@@ -20519,10 +23472,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.74</v>
+        <v>15.3</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:11">
@@ -20533,19 +23486,19 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1.2982</v>
+        <v>24.4</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>1.2475666666666667</v>
-      </c>
-      <c r="E5" s="6">
+        <v>23.866666666666664</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>7.8366468169321829E-2</v>
+        <v>1.4742229591663989</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>4.5298536514058858E-2</v>
+        <v>0.85215199951814968</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -20556,10 +23509,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1.2871999999999999</v>
+        <v>25</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:11">
@@ -20570,10 +23523,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1.1573</v>
+        <v>22.2</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:11">
@@ -20584,25 +23537,25 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1.0165999999999999</v>
+        <v>25.7</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>1.0533000000000001</v>
-      </c>
-      <c r="E8" s="6">
+        <v>24.766666666666666</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>6.3047363148667893E-2</v>
+        <v>0.86216781042517032</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>3.6443562513680861E-2</v>
+        <v>0.4983628961995204</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -20613,21 +23566,21 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>1.1261000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="I9" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="1">
         <f>D2</f>
-        <v>0.73999999999999988</v>
+        <v>14.9</v>
       </c>
       <c r="K9">
         <f>E2</f>
-        <v>7.0000000000000007E-2</v>
+        <v>0.78102496759066575</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -20638,21 +23591,21 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>1.0172000000000001</v>
+        <v>24</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="I10" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="1">
         <f>D5</f>
-        <v>1.2475666666666667</v>
+        <v>23.866666666666664</v>
       </c>
       <c r="K10">
         <f>E5</f>
-        <v>7.8366468169321829E-2</v>
+        <v>1.4742229591663989</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -20663,30 +23616,30 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1.2674000000000001</v>
+        <v>24</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>1.2407000000000001</v>
-      </c>
-      <c r="E11" s="6">
+        <v>22.7</v>
+      </c>
+      <c r="E11" s="7">
         <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>2.51334438547526E-2</v>
+        <v>1.1532562594670792</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>1.4528002228180695E-2</v>
+        <v>0.66662211529888971</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="1">
         <f>D8</f>
-        <v>1.0533000000000001</v>
+        <v>24.766666666666666</v>
       </c>
       <c r="K11">
         <f>E8</f>
-        <v>6.3047363148667893E-2</v>
+        <v>0.86216781042517032</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -20697,21 +23650,21 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>1.2175</v>
+        <v>22.3</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="I12" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="1">
         <f>D11</f>
-        <v>1.2407000000000001</v>
+        <v>22.7</v>
       </c>
       <c r="K12">
         <f>E11</f>
-        <v>2.51334438547526E-2</v>
+        <v>1.1532562594670792</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -20722,21 +23675,21 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>1.2372000000000001</v>
+        <v>21.8</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" s="1">
         <f>D14</f>
-        <v>1.3037666666666665</v>
+        <v>28.7</v>
       </c>
       <c r="K13">
         <f>E14</f>
-        <v>1.1547438388375733E-2</v>
+        <v>1.2124355652982151</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -20747,19 +23700,19 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>1.2971999999999999</v>
+        <v>28.9</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>1.3037666666666665</v>
-      </c>
-      <c r="E14" s="6">
+        <v>28.7</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>1.1547438388375733E-2</v>
+        <v>1.2124355652982151</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>6.674819877673834E-3</v>
+        <v>0.7008298065307601</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -20770,10 +23723,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>1.3170999999999999</v>
+        <v>29.8</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:11">
@@ -20784,10 +23737,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1.2969999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
   </sheetData>
@@ -20814,8 +23767,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049DAB7E-34A2-4711-BCDA-47CE19215AC4}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02FBF418-3FED-43A6-B6C8-3E3A43CED8D9}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -20831,7 +23784,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -20851,19 +23804,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>0.88200000000000001</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D2" s="6">
         <f>AVERAGE(C2:C4)</f>
-        <v>0.84199999999999997</v>
-      </c>
-      <c r="E2" s="6">
+        <v>10.533333333333333</v>
+      </c>
+      <c r="E2" s="7">
         <f>STDEV(C2:C4)</f>
-        <v>7.5425459892532312E-2</v>
+        <v>0.64291005073286345</v>
       </c>
       <c r="F2" s="7">
         <f>E2/1.73</f>
-        <v>4.3598531729787462E-2</v>
+        <v>0.37162430678200198</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -20874,10 +23827,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0.88900000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:11">
@@ -20888,10 +23841,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.755</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:11">
@@ -20902,19 +23855,19 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1.171</v>
+        <v>11.3</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>1.113</v>
-      </c>
-      <c r="E5" s="6">
+        <v>12.233333333333334</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>5.302829433425145E-2</v>
+        <v>0.86216781042517054</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>3.0652193256792745E-2</v>
+        <v>0.49836289619952057</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -20925,10 +23878,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1.0669999999999999</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:11">
@@ -20939,10 +23892,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1.101</v>
+        <v>12.4</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:11">
@@ -20953,25 +23906,25 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1.02</v>
+        <v>13.2</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>0.96500000000000019</v>
-      </c>
-      <c r="E8" s="6">
+        <v>11.866666666666667</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>0.14930170796075776</v>
+        <v>1.1718930554164626</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>8.6301565295235694E-2</v>
+        <v>0.67739482972049858</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -20982,21 +23935,21 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>1.079</v>
+        <v>11.4</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="I9" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="1">
         <f>D2</f>
-        <v>0.84199999999999997</v>
+        <v>10.533333333333333</v>
       </c>
       <c r="K9">
         <f>E2</f>
-        <v>7.5425459892532312E-2</v>
+        <v>0.64291005073286345</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -21007,21 +23960,21 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>0.79600000000000004</v>
+        <v>11</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="I10" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="1">
         <f>D5</f>
-        <v>1.113</v>
+        <v>12.233333333333334</v>
       </c>
       <c r="K10">
         <f>E5</f>
-        <v>5.302829433425145E-2</v>
+        <v>0.86216781042517054</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -21032,30 +23985,30 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>1.1970000000000001</v>
+        <v>14</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>1.133</v>
-      </c>
-      <c r="E11" s="6">
+        <v>12.266666666666666</v>
+      </c>
+      <c r="E11" s="7">
         <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>5.8923679450624995E-2</v>
+        <v>1.6165807537309642</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>3.4059930318280342E-2</v>
+        <v>0.93443974204101976</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="1">
         <f>D8</f>
-        <v>0.96500000000000019</v>
+        <v>11.866666666666667</v>
       </c>
       <c r="K11">
         <f>E8</f>
-        <v>0.14930170796075776</v>
+        <v>1.1718930554164626</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -21066,21 +24019,21 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>1.081</v>
+        <v>10.8</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="I12" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="1">
         <f>D11</f>
-        <v>1.133</v>
+        <v>12.266666666666666</v>
       </c>
       <c r="K12">
         <f>E11</f>
-        <v>5.8923679450624995E-2</v>
+        <v>1.6165807537309642</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -21091,21 +24044,21 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>1.121</v>
+        <v>12</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" s="1">
         <f>D14</f>
-        <v>1.1200000000000001</v>
+        <v>14.200000000000001</v>
       </c>
       <c r="K13">
         <f>E14</f>
-        <v>2.4248711305964205E-2</v>
+        <v>1.1532562594670792</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -21116,19 +24069,19 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>1.1419999999999999</v>
+        <v>15.1</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="E14" s="6">
+        <v>14.200000000000001</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>2.4248711305964205E-2</v>
+        <v>1.1532562594670792</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>1.4016596130615148E-2</v>
+        <v>0.66662211529888971</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -21139,10 +24092,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>1.1240000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:11">
@@ -21153,10 +24106,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1.0940000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
   </sheetData>
@@ -21183,8 +24136,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC084203-75CD-44F8-9605-0E76FFF67A2B}">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7C68FA-467F-45D6-ACDA-122C417EA1D9}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -21200,7 +24153,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -21220,19 +24173,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>9.7000000000000003E-2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="6">
         <f>AVERAGE(C2:C4)</f>
-        <v>9.5000000000000015E-2</v>
-      </c>
-      <c r="E2" s="6">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="E2" s="7">
         <f>STDEV(C2:C4)</f>
-        <v>5.2915026221291859E-3</v>
+        <v>0.57735026918962584</v>
       </c>
       <c r="F2" s="7">
         <f>E2/1.73</f>
-        <v>3.0586720359128241E-3</v>
+        <v>0.33372847930036176</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -21243,10 +24196,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>9.9000000000000005E-2</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:11">
@@ -21257,10 +24210,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>8.8999999999999996E-2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:11">
@@ -21271,19 +24224,19 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0.13100000000000001</v>
+        <v>3</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="E5" s="6">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>2.0000000000000018E-3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>1.1560693641618507E-3</v>
+        <v>0.5780346820809249</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -21294,10 +24247,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0.13300000000000001</v>
+        <v>2</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:11">
@@ -21308,13 +24261,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>0.129</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="19.5" customHeight="1">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>3</v>
       </c>
@@ -21322,25 +24275,25 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.121</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6">
         <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>0.11566666666666665</v>
-      </c>
-      <c r="E8" s="6">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>7.5718777944003635E-3</v>
+        <v>1.1547005383792515</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>4.3768079736418285E-3</v>
+        <v>0.6674569586007234</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -21351,21 +24304,21 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>0.11899999999999999</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="I9" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="1">
         <f>D2</f>
-        <v>9.5000000000000015E-2</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="K9">
         <f>E2</f>
-        <v>5.2915026221291859E-3</v>
+        <v>0.57735026918962584</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -21376,21 +24329,21 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>0.107</v>
+        <v>1</v>
       </c>
       <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="I10" t="s">
         <v>9</v>
       </c>
       <c r="J10" s="1">
         <f>D5</f>
-        <v>0.13100000000000001</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <f>E5</f>
-        <v>2.0000000000000018E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -21401,30 +24354,30 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.152</v>
+        <v>1</v>
       </c>
       <c r="D11" s="6">
         <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>0.13066666666666668</v>
-      </c>
-      <c r="E11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7">
         <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>2.0550750189064392E-2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>1.1879046352060342E-2</v>
+        <v>0.5780346820809249</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="1">
         <f>D8</f>
-        <v>0.11566666666666665</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="K11">
         <f>E8</f>
-        <v>7.5718777944003635E-3</v>
+        <v>1.1547005383792515</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -21435,21 +24388,21 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>0.129</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="I12" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="1">
         <f>D11</f>
-        <v>0.13066666666666668</v>
+        <v>2</v>
       </c>
       <c r="K12">
         <f>E11</f>
-        <v>2.0550750189064392E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -21460,21 +24413,21 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>0.111</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="I13" t="s">
         <v>12</v>
       </c>
       <c r="J13" s="1">
         <f>D14</f>
-        <v>0.16033333333333333</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="K13">
         <f>E14</f>
-        <v>2.7227437142216249E-2</v>
+        <v>0.57735026918962473</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -21485,19 +24438,19 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>0.191</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6">
         <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>0.16033333333333333</v>
-      </c>
-      <c r="E14" s="6">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>2.7227437142216249E-2</v>
+        <v>0.57735026918962473</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>1.5738402972379335E-2</v>
+        <v>0.33372847930036115</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -21508,10 +24461,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>0.13900000000000001</v>
+        <v>3</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:11">
@@ -21522,10 +24475,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>0.151</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
   </sheetData>
@@ -21552,8 +24505,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975E62B9-E4A7-4D06-8781-56D58217A609}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E1FD06-7056-4AEF-8AEB-D3FD515BEB8E}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -21569,7 +24522,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -21589,19 +24542,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D2" s="8">
+        <v>37</v>
+      </c>
+      <c r="D2" s="6">
         <f>AVERAGE(C2:C4)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="E2" s="8">
+        <v>36.333333333333336</v>
+      </c>
+      <c r="E2" s="7">
         <f>STDEV(C2:C4)</f>
-        <v>5.000000000000001E-3</v>
+        <v>2.0816659994661326</v>
       </c>
       <c r="F2" s="7">
         <f>E2/1.73</f>
-        <v>2.890173410404625E-3</v>
+        <v>1.2032751442000766</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -21612,10 +24565,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>0.01</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+        <v>34</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:11">
@@ -21626,10 +24579,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.02</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+        <v>38</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:11">
@@ -21640,19 +24593,19 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="D5" s="8">
+        <v>51</v>
+      </c>
+      <c r="D5" s="6">
         <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>3.8666666666666669E-2</v>
-      </c>
-      <c r="E5" s="8">
+        <v>50</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>6.1101009266077855E-3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7">
         <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>3.5318502465940958E-3</v>
+        <v>0.5780346820809249</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -21663,10 +24616,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0.04</v>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:11">
@@ -21677,13 +24630,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+        <v>49</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="19.5" customHeight="1">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>3</v>
       </c>
@@ -21691,25 +24644,25 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="D8" s="8">
+        <v>43</v>
+      </c>
+      <c r="D8" s="6">
         <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>0.14233333333333334</v>
-      </c>
-      <c r="E8" s="8">
+        <v>44.333333333333336</v>
+      </c>
+      <c r="E8" s="7">
         <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>7.76745346515402E-3</v>
+        <v>4.1633319989322661</v>
       </c>
       <c r="F8" s="7">
         <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>4.4898574943086824E-3</v>
+        <v>2.4065502884001537</v>
       </c>
       <c r="I8" t="s">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -21720,21 +24673,21 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>0.151</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+        <v>49</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="I9" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="1">
         <f>D2</f>
-        <v>1.4999999999999999E-2</v>
+        <v>36.333333333333336</v>
       </c>
       <c r="K9">
         <f>E2</f>
-        <v>5.000000000000001E-3</v>
+        <v>2.0816659994661326</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -21745,21 +24698,21 @@
         <v>3</v>
       </c>
       <c r="C10">
-        <v>0.13600000000000001</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+        <v>41</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="I10" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="1">
         <f>D5</f>
-        <v>3.8666666666666669E-2</v>
+        <v>50</v>
       </c>
       <c r="K10">
         <f>E5</f>
-        <v>6.1101009266077855E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -21770,30 +24723,30 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.125</v>
-      </c>
-      <c r="D11" s="8">
+        <v>48</v>
+      </c>
+      <c r="D11" s="6">
         <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>0.11833333333333333</v>
-      </c>
-      <c r="E11" s="8">
+        <v>48.333333333333336</v>
+      </c>
+      <c r="E11" s="7">
         <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>7.6376261582597324E-3</v>
+        <v>1.5275252316519465</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>4.4148128082426201E-3</v>
+        <v>0.88296256164852405</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="1">
         <f>D8</f>
-        <v>0.14233333333333334</v>
+        <v>44.333333333333336</v>
       </c>
       <c r="K11">
         <f>E8</f>
-        <v>7.76745346515402E-3</v>
+        <v>4.1633319989322661</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -21804,21 +24757,21 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>0.11</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="I12" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="1">
         <f>D11</f>
-        <v>0.11833333333333333</v>
+        <v>48.333333333333336</v>
       </c>
       <c r="K12">
         <f>E11</f>
-        <v>7.6376261582597324E-3</v>
+        <v>1.5275252316519465</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -21829,21 +24782,21 @@
         <v>3</v>
       </c>
       <c r="C13">
-        <v>0.12</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+        <v>50</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="I13" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="1">
         <f>D14</f>
-        <v>0.19033333333333333</v>
+        <v>77.333333333333329</v>
       </c>
       <c r="K13">
         <f>E14</f>
-        <v>7.2341781380702418E-3</v>
+        <v>1.5275252316519468</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -21854,19 +24807,19 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="D14" s="8">
+        <v>77</v>
+      </c>
+      <c r="D14" s="6">
         <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>0.19033333333333333</v>
-      </c>
-      <c r="E14" s="8">
+        <v>77.333333333333329</v>
+      </c>
+      <c r="E14" s="7">
         <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>7.2341781380702418E-3</v>
+        <v>1.5275252316519468</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>4.181605860156209E-3</v>
+        <v>0.88296256164852416</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -21877,10 +24830,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>0.19400000000000001</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+        <v>79</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:11">
@@ -21891,10 +24844,10 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>0.182</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+        <v>76</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
   </sheetData>
@@ -21919,3076 +24872,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53F62340-CD4B-4BE3-B13A-8440BC2B3C42}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>4.6050000000000004</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>3.726452736853104</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>2.1540189230364764</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1.97</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>7.24</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>5.13</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>3.4899999999999998</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>2.686186888509436</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>1.5527091841095007</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>0.39</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>4.95</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>2.73</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>2.6</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>1.2500799974401644</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>0.72258959389604882</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>3.78</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>4.6050000000000004</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>3.726452736853104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1.29</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>3.4899999999999998</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>2.686186888509436</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>4.2300000000000004</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>2.0454583838347826</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>1.182345886609701</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>2.6</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>1.2500799974401644</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>1.07</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>2.0454583838347826</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>1.07</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>1.1170049238924598</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>0.63</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>1.07</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>1.1170049238924598</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.64566758606500563</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>0.24</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>2.34</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F91474D-2594-4106-AE97-A03B90325336}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>28</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>28</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>4</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>2.3121387283236996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>24</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>32</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>22</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>2.3094010767585034</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>1.334913917201447</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>26</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>21</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>2.0816659994661331</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>1.2032751442000769</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>22</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>28</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>18</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>24.666666666666668</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>2.3094010767585034</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>24</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>17.333333333333332</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>6.1101009266077853</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>3.5318502465940957</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>20.333333333333332</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>2.0816659994661331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>16</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>17.333333333333332</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>6.1101009266077853</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>18</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>8.8881944173155887</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>28</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>18</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>8.8881944173155887</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>5.1376846342864679</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>15</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>11</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D3B4B9-8DED-4B73-93B7-BCD80CB04959}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>2.6966666666666668</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>0.59601454120963582</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>0.34451707584372016</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3.08</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3.1</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>3.2833333333333332</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>0.31754264805429405</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>0.18355066361519887</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>3.1</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>3.65</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3.6</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>3.6999999999999997</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>0.26457513110645903</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>0.15293360179564106</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>3.5</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>2.6966666666666668</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>0.59601454120963582</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>3.2833333333333332</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>0.31754264805429405</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>3.9</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>3.56</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>0.50477717856495796</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>0.29177871593350174</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>3.6999999999999997</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>0.26457513110645903</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>3.8</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>3.56</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>0.50477717856495796</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>2.98</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>0.66583281184793797</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>2.9</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>0.66583281184793797</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.38487445771557111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDA2AF0-16A6-4B39-87FB-8E571EBB2CCD}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>0.78666666666666674</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>0.10503967504392438</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>6.0716575169898486E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0.89</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>0.79</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1.2</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>1.0733333333333335</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>0.15534906930308059</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>8.9797149886173752E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>0.9</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1.3</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>0.15620499351813161</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>9.0291903767706128E-2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>1.02</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>0.78666666666666674</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>0.10503967504392438</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1.28</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>1.0733333333333335</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>0.15534906930308059</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1.22</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>1.5733333333333333</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>0.31005375877956043</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>0.17922182588413899</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>0.15620499351813161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>1.8</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>1.5733333333333333</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>0.31005375877956043</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>1.7</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>1.7</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>0.26457513110645958</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1.8</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>1.7</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>0.26457513110645958</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.15293360179564139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>1.4</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>1.9</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{376CE82E-C44D-4C61-BB92-E28C40E3BFA2}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>14</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>14.9</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>0.78102496759066575</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>0.45145951883853513</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>15.4</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>15.3</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>24.4</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>23.866666666666664</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>1.4742229591663989</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>0.85215199951814968</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>22.2</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>25.7</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>24.766666666666666</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>0.86216781042517032</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>0.4983628961995204</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>24.6</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>14.9</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>0.78102496759066575</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>24</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>23.866666666666664</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>1.4742229591663989</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>24</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>22.7</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>1.1532562594670792</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>0.66662211529888971</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>24.766666666666666</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>0.86216781042517032</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>22.3</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>22.7</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>1.1532562594670792</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>21.8</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>28.7</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>1.2124355652982151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>28.9</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>28.7</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>1.2124355652982151</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.7008298065307601</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>29.8</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>27.4</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02FBF418-3FED-43A6-B6C8-3E3A43CED8D9}">
-  <dimension ref="A1:O44"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>10.533333333333333</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>0.64291005073286345</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>0.37162430678200198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>10.8</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>11</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>11.3</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>12.233333333333334</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>0.86216781042517054</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>0.49836289619952057</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>12.4</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>13.2</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>11.866666666666667</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>1.1718930554164626</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>0.67739482972049858</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>11.4</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>10.533333333333333</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>0.64291005073286345</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>11</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>12.233333333333334</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>0.86216781042517054</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>14</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>12.266666666666666</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>1.6165807537309642</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>0.93443974204101976</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>11.866666666666667</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>1.1718930554164626</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>10.8</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>12.266666666666666</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>1.6165807537309642</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>14.200000000000001</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>1.1532562594670792</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>15.1</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>14.200000000000001</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>1.1532562594670792</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.66662211529888971</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>12.9</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>14.6</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="B27">
-        <v>10.8</v>
-      </c>
-      <c r="C27">
-        <v>11</v>
-      </c>
-      <c r="D27">
-        <v>11.3</v>
-      </c>
-      <c r="E27">
-        <v>13</v>
-      </c>
-      <c r="F27">
-        <v>12.4</v>
-      </c>
-      <c r="G27">
-        <v>13.2</v>
-      </c>
-      <c r="H27">
-        <v>11.4</v>
-      </c>
-      <c r="I27">
-        <v>11</v>
-      </c>
-      <c r="J27">
-        <v>14</v>
-      </c>
-      <c r="K27">
-        <v>10.8</v>
-      </c>
-      <c r="L27">
-        <v>12</v>
-      </c>
-      <c r="M27">
-        <v>15.1</v>
-      </c>
-      <c r="N27">
-        <v>12.9</v>
-      </c>
-      <c r="O27">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="C30">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
-      <c r="C31">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
-      <c r="C32">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3">
-      <c r="C37">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="38" spans="3:3">
-      <c r="C38">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3">
-      <c r="C39">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="41" spans="3:3">
-      <c r="C41">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="3:3">
-      <c r="C42">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="43" spans="3:3">
-      <c r="C43">
-        <v>12.9</v>
-      </c>
-    </row>
-    <row r="44" spans="3:3">
-      <c r="C44">
-        <v>14.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7C68FA-467F-45D6-ACDA-122C417EA1D9}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>0.57735026918962584</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>0.33372847930036176</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>2</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>0.5780346820809249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>1.1547005383792515</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>0.6674569586007234</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>0.57735026918962584</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>2</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>2</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>1</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>0.5780346820809249</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>1.1547005383792515</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>2</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>0.57735026918962473</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>0.57735026918962473</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.33372847930036115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E1FD06-7056-4AEF-8AEB-D3FD515BEB8E}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>37</v>
-      </c>
-      <c r="D2" s="6">
-        <f>AVERAGE(C2:C4)</f>
-        <v>36.333333333333336</v>
-      </c>
-      <c r="E2" s="7">
-        <f>STDEV(C2:C4)</f>
-        <v>2.0816659994661326</v>
-      </c>
-      <c r="F2" s="7">
-        <f>E2/1.73</f>
-        <v>1.2032751442000766</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>34</v>
-      </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>38</v>
-      </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>51</v>
-      </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5" si="0">AVERAGE(C5:C7)</f>
-        <v>50</v>
-      </c>
-      <c r="E5" s="7">
-        <f t="shared" ref="E5" si="1">STDEV(C5:C7)</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="7">
-        <f t="shared" ref="F5" si="2">E5/1.73</f>
-        <v>0.5780346820809249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>50</v>
-      </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>49</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>43</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" ref="D8" si="3">AVERAGE(C8:C10)</f>
-        <v>44.333333333333336</v>
-      </c>
-      <c r="E8" s="7">
-        <f t="shared" ref="E8" si="4">STDEV(C8:C10)</f>
-        <v>4.1633319989322661</v>
-      </c>
-      <c r="F8" s="7">
-        <f t="shared" ref="F8" si="5">E8/1.73</f>
-        <v>2.4065502884001537</v>
-      </c>
-      <c r="I8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>49</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
-        <f>D2</f>
-        <v>36.333333333333336</v>
-      </c>
-      <c r="K9">
-        <f>E2</f>
-        <v>2.0816659994661326</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>41</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="1">
-        <f>D5</f>
-        <v>50</v>
-      </c>
-      <c r="K10">
-        <f>E5</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>48</v>
-      </c>
-      <c r="D11" s="6">
-        <f t="shared" ref="D11" si="6">AVERAGE(C11:C13)</f>
-        <v>48.333333333333336</v>
-      </c>
-      <c r="E11" s="7">
-        <f t="shared" ref="E11" si="7">STDEV(C11:C13)</f>
-        <v>1.5275252316519465</v>
-      </c>
-      <c r="F11" s="7">
-        <f t="shared" ref="F11" si="8">E11/1.73</f>
-        <v>0.88296256164852405</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1">
-        <f>D8</f>
-        <v>44.333333333333336</v>
-      </c>
-      <c r="K11">
-        <f>E8</f>
-        <v>4.1633319989322661</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>47</v>
-      </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="I12" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="1">
-        <f>D11</f>
-        <v>48.333333333333336</v>
-      </c>
-      <c r="K12">
-        <f>E11</f>
-        <v>1.5275252316519465</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>50</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="I13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1">
-        <f>D14</f>
-        <v>77.333333333333329</v>
-      </c>
-      <c r="K13">
-        <f>E14</f>
-        <v>1.5275252316519468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>77</v>
-      </c>
-      <c r="D14" s="6">
-        <f t="shared" ref="D14" si="9">AVERAGE(C14:C16)</f>
-        <v>77.333333333333329</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" ref="E14" si="10">STDEV(C14:C16)</f>
-        <v>1.5275252316519468</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" ref="F14" si="11">E14/1.73</f>
-        <v>0.88296256164852416</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>79</v>
-      </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>76</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>